--- a/static/data/phantom_pronouns_lev_1.xlsx
+++ b/static/data/phantom_pronouns_lev_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ACA0A008A5DDF25F/course_app/static/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="507" documentId="8_{23FE63F9-F8A8-4024-A980-EB15DF25DEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{762F5E3B-F450-4DAA-B4E8-8CF5B61F7F9D}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="8_{23FE63F9-F8A8-4024-A980-EB15DF25DEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3901D1BB-7F7A-4974-A831-2141E630F70B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1D4F141B-7D6F-4B5C-8F23-9694E650866C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="238">
   <si>
     <t>I</t>
   </si>
@@ -80,12 +80,6 @@
     <t>les</t>
   </si>
   <si>
-    <t>los</t>
-  </si>
-  <si>
-    <t>las</t>
-  </si>
-  <si>
     <t>lo</t>
   </si>
   <si>
@@ -128,21 +122,9 @@
     <t>spanish for object you (*plural)</t>
   </si>
   <si>
-    <t>spanish for object you (*plural)2</t>
-  </si>
-  <si>
-    <t>spanish for object you (*plural)3</t>
-  </si>
-  <si>
     <t>spanish for object them</t>
   </si>
   <si>
-    <t>spanish for object them2</t>
-  </si>
-  <si>
-    <t>spanish for object them3</t>
-  </si>
-  <si>
     <t>spanish for object him</t>
   </si>
   <si>
@@ -155,9 +137,6 @@
     <t>spanish for object her2</t>
   </si>
   <si>
-    <t>spanish for object it</t>
-  </si>
-  <si>
     <t>spanish for object it2</t>
   </si>
   <si>
@@ -168,12 +147,6 @@
   </si>
   <si>
     <t>mire</t>
-  </si>
-  <si>
-    <t>spanish for object you (*singular)3</t>
-  </si>
-  <si>
-    <t>spanish for object you (*singular)4</t>
   </si>
   <si>
     <t>note</t>
@@ -786,7 +759,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,37 +796,16 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor theme="7" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -861,31 +813,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="7"/>
-      </top>
-      <bottom style="thin">
-        <color theme="7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -899,18 +831,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1678,20 +1598,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B30FC44-8AF0-4830-9D28-CEA47D84CB50}">
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AQ105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16" width="2.109375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="37.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="34.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="31.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="32.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="30.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="30" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="35.44140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" s="1" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1710,72 +1637,86 @@
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-    </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+    </row>
+    <row r="2" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1795,48 +1736,50 @@
         <v>10</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3"/>
-      <c r="S3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AL3" s="2"/>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+    </row>
+    <row r="4" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1856,48 +1799,50 @@
         <v>10</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4"/>
-      <c r="S4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1914,40 +1859,50 @@
         <v>10</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Z5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,40 +1919,50 @@
         <v>10</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N6"/>
       <c r="O6"/>
       <c r="P6"/>
       <c r="Q6"/>
       <c r="R6"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Z6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC6" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -2023,48 +1988,50 @@
         <v>10</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N7"/>
       <c r="O7"/>
       <c r="P7"/>
       <c r="Q7"/>
       <c r="R7"/>
-      <c r="S7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="W7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC7" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="2"/>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="2"/>
+      <c r="AL7" s="2"/>
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="2"/>
+      <c r="AO7" s="2"/>
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
+    </row>
+    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -2090,48 +2057,50 @@
         <v>10</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N8"/>
       <c r="O8"/>
       <c r="P8"/>
       <c r="Q8"/>
       <c r="R8"/>
-      <c r="S8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="X8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC8" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="2"/>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="2"/>
+      <c r="AM8" s="2"/>
+      <c r="AN8" s="2"/>
+      <c r="AO8" s="2"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+    </row>
+    <row r="9" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -2157,48 +2126,50 @@
         <v>10</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N9"/>
       <c r="O9"/>
       <c r="P9"/>
       <c r="Q9"/>
       <c r="R9"/>
-      <c r="S9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="W9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC9" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+    </row>
+    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -2224,208 +2195,258 @@
         <v>10</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N10"/>
       <c r="O10"/>
       <c r="P10"/>
       <c r="Q10"/>
       <c r="R10"/>
-      <c r="S10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="T10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="X10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA10" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC10" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" ht="18" x14ac:dyDescent="0.35">
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="2"/>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="2"/>
+      <c r="AL10" s="2"/>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="2"/>
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="2"/>
+      <c r="AG11" s="2"/>
+      <c r="AH11" s="2"/>
+      <c r="AI11" s="2"/>
+      <c r="AJ11" s="2"/>
+      <c r="AK11" s="2"/>
+      <c r="AL11" s="2"/>
+      <c r="AM11" s="2"/>
+      <c r="AN11" s="2"/>
+      <c r="AO11" s="2"/>
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+    </row>
+    <row r="12" spans="1:43" ht="18" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="2"/>
+      <c r="AG12" s="2"/>
+      <c r="AH12" s="2"/>
+      <c r="AI12" s="2"/>
+      <c r="AJ12" s="2"/>
+      <c r="AK12" s="2"/>
+      <c r="AL12" s="2"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="2"/>
+      <c r="AO12" s="2"/>
+      <c r="AP12" s="2"/>
+      <c r="AQ12" s="2"/>
+    </row>
+    <row r="13" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -2433,33 +2454,33 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -2467,33 +2488,33 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2501,33 +2522,33 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -2535,33 +2556,33 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -2569,33 +2590,33 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -2603,33 +2624,33 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -2637,33 +2658,33 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -2671,33 +2692,33 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
@@ -2705,258 +2726,258 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="Q31" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="Q33" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -2965,769 +2986,769 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="F38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="F46" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O49" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O55" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O59" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
@@ -3736,1265 +3757,1265 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="F95" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="F97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="F98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
